--- a/artfynd/A 45851-2022 artfynd.xlsx
+++ b/artfynd/A 45851-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45851-2022 artfynd.xlsx
+++ b/artfynd/A 45851-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,39 +675,30 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89215392</v>
+        <v>89215394</v>
       </c>
       <c r="B2" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3762</v>
+        <v>433</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -715,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665830.0905990878</v>
+        <v>665847</v>
       </c>
       <c r="R2" t="n">
-        <v>6710944.129396567</v>
+        <v>6711071</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -748,19 +739,9 @@
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +768,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89215411</v>
+        <v>89215409</v>
       </c>
       <c r="B3" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>473</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665747.2314850506</v>
+        <v>665786</v>
       </c>
       <c r="R3" t="n">
-        <v>6710919.112018492</v>
+        <v>6711001</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -860,19 +836,9 @@
           <t>2020-10-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,6 +862,297 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>89215411</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91680</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Uppland, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>665747</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6710919</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-10-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-10-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Barbara Kühn</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Barbara Kühn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>89215392</v>
+      </c>
+      <c r="B5" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Uppland, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>665830</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6710944</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-10-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-10-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Barbara Kühn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Barbara Kühn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>89215406</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Uppland, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>665792</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6711021</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-10-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-10-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Barbara Kühn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Barbara Kühn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45851-2022 artfynd.xlsx
+++ b/artfynd/A 45851-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -765,6 +770,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89215394</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -862,6 +872,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89215409</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -959,6 +974,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89215411</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1056,6 +1076,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89215392</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1153,8 +1178,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89215406</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>